--- a/DC_Content_Rule_Catalog.xlsx
+++ b/DC_Content_Rule_Catalog.xlsx
@@ -16312,7 +16312,7 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>(threat.category = 'llm-provider','llm-enterprise','llm-coding') &amp;&amp; (tcp.dstport = 443 || tcp.dstport = 80 || tcp.dstport = 8080 || tcp.dstport = 8443 || tcp.dstport = 3128) &amp;&amp; client exists &amp;&amp; NOT client contains 'Mozilla/'</t>
+          <t>(threat.category = 'llm-provider','llm-enterprise','llm-coding') &amp;&amp; (tcp.dstport = 443 || tcp.dstport = 80 || tcp.dstport = 8080 || tcp.dstport = 8443 || tcp.dstport = 3128) &amp;&amp; client exists &amp;&amp; not(client contains 'Mozilla/')</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
